--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6608</v>
+        <v>17.5439</v>
       </c>
       <c r="E2" t="n">
-        <v>8.754999999999999</v>
+        <v>8.1928</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9057</v>
+        <v>9.351000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1224</v>
+        <v>2.8076</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4609</v>
+        <v>2.1138</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6616</v>
+        <v>0.6940000000000002</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0951</v>
+        <v>5.278899999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3562</v>
+        <v>3.1284</v>
       </c>
       <c r="L2" t="n">
-        <v>2.738599999999999</v>
+        <v>2.1505</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9724</v>
+        <v>-2.4713</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8953</v>
+        <v>-1.0147</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.077</v>
+        <v>-1.4566</v>
       </c>
       <c r="P2" t="n">
-        <v>2.663</v>
+        <v>3.6442</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.555099999999999</v>
+        <v>-7.693199999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.2181</v>
+        <v>11.3374</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6714</v>
+        <v>1.6467</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5731</v>
+        <v>0.7699</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09820000000000007</v>
+        <v>0.8765000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>8.203900000000001</v>
+        <v>9.445599999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>8.642200000000001</v>
+        <v>9.837</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4382999999999999</v>
+        <v>-0.3913999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>10.2885</v>
+        <v>13.5187</v>
       </c>
       <c r="E3" t="n">
-        <v>9.284799999999999</v>
+        <v>11.6441</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0036</v>
+        <v>1.8746</v>
       </c>
       <c r="G3" t="n">
-        <v>19.2157</v>
+        <v>22.6653</v>
       </c>
       <c r="H3" t="n">
-        <v>8.1701</v>
+        <v>10.8111</v>
       </c>
       <c r="I3" t="n">
-        <v>11.0454</v>
+        <v>11.8543</v>
       </c>
       <c r="J3" t="n">
-        <v>24.9703</v>
+        <v>27.9416</v>
       </c>
       <c r="K3" t="n">
-        <v>11.2675</v>
+        <v>14.336</v>
       </c>
       <c r="L3" t="n">
-        <v>13.7028</v>
+        <v>13.6055</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.7546</v>
+        <v>-5.2762</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.0972</v>
+        <v>-3.525</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.6572</v>
+        <v>-1.7512</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.0726</v>
+        <v>-3.4418</v>
       </c>
       <c r="Q3" t="n">
-        <v>-11.8812</v>
+        <v>-13.9692</v>
       </c>
       <c r="R3" t="n">
-        <v>8.808400000000001</v>
+        <v>10.5276</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.3256</v>
+        <v>-2.705</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.1822</v>
+        <v>-3.5831</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1433</v>
+        <v>0.8780000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5288</v>
+        <v>-2.9999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3781</v>
+        <v>1.2545</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9069</v>
+        <v>-4.2545</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.827500000000001</v>
+        <v>4.1082</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5216</v>
+        <v>-1.0482</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3057</v>
+        <v>5.1563</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9667</v>
+        <v>1.999200000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4483</v>
+        <v>2.6907</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5182000000000004</v>
+        <v>-0.6914999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>6.1601</v>
+        <v>6.391900000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1238</v>
+        <v>4.3987</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0362</v>
+        <v>1.9932</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.1934</v>
+        <v>-4.3927</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6754</v>
+        <v>-1.7082</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.518</v>
+        <v>-2.6847</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0242</v>
+        <v>1.2148</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.5551</v>
+        <v>-8.705500000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>7.5793</v>
+        <v>9.920199999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>2.301600000000001</v>
+        <v>3.0612</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2519</v>
+        <v>0.2616999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>2.0497</v>
+        <v>2.7996</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4652</v>
+        <v>-2.1667</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6648</v>
+        <v>1.0037</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.1299</v>
+        <v>-3.1705</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1703</v>
+        <v>1.6484</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2673</v>
+        <v>1.0079</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9029</v>
+        <v>0.6406999999999998</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7225</v>
+        <v>3.4493</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4685</v>
+        <v>1.2677</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2541</v>
+        <v>2.1819</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7493</v>
+        <v>2.3564</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2146</v>
+        <v>0.3161</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5346</v>
+        <v>2.0403</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.0931</v>
       </c>
       <c r="N5" t="n">
-        <v>1.2539</v>
+        <v>0.9514</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2805</v>
+        <v>0.1417</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6145</v>
+        <v>-0.2025000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0484</v>
+        <v>-2.2271</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4339</v>
+        <v>2.0246</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1236</v>
+        <v>-0.2261999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3860000000000001</v>
+        <v>-0.3117</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2622999999999999</v>
+        <v>0.08560000000000012</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9385000000000001</v>
+        <v>-1.3723</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2421</v>
+        <v>-2.5625</v>
       </c>
     </row>
     <row r="6">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1666</v>
+        <v>1.132100000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.446600000000001</v>
+        <v>2.7308</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2798</v>
+        <v>-1.5987</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.964</v>
+        <v>-1.7513</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0892</v>
+        <v>2.3937</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0532</v>
+        <v>-4.1449</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6325</v>
+        <v>3.1619</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3776</v>
+        <v>5.0519</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7450999999999999</v>
+        <v>-1.8899</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.5964</v>
+        <v>-4.9133</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2883</v>
+        <v>-2.6582</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.3079</v>
+        <v>-2.255</v>
       </c>
       <c r="P6" t="n">
-        <v>1.434</v>
+        <v>1.6196</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.555100000000001</v>
+        <v>-7.4908</v>
       </c>
       <c r="R6" t="n">
-        <v>7.989100000000001</v>
+        <v>9.110300000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7749000000000001</v>
+        <v>1.0774</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7848</v>
+        <v>1.7324</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0099</v>
+        <v>-0.6550999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>2.9218</v>
+        <v>0.1863999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>5.5844</v>
+        <v>5.3271</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6626</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="7">
@@ -955,22 +955,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.159</v>
+        <v>0.1576</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.159</v>
+        <v>0.1576</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0196</v>
+        <v>0.0192</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0196</v>
+        <v>0.0192</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3676999999999997</v>
+        <v>-2.0786</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2427</v>
+        <v>0.3626999999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6103</v>
+        <v>-2.4411</v>
       </c>
       <c r="G8" t="n">
-        <v>8.597499999999998</v>
+        <v>5.909699999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5151</v>
+        <v>-4.1525</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0824</v>
+        <v>10.0621</v>
       </c>
       <c r="J8" t="n">
-        <v>8.456</v>
+        <v>11.8782</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7401</v>
+        <v>-2.029</v>
       </c>
       <c r="L8" t="n">
-        <v>3.716</v>
+        <v>13.9071</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1415</v>
+        <v>-5.9686</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2247999999999999</v>
+        <v>-2.1234</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3665000000000002</v>
+        <v>-3.845</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8194000000000001</v>
+        <v>-10.5275</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.1454</v>
+        <v>-20.65</v>
       </c>
       <c r="R8" t="n">
-        <v>6.9648</v>
+        <v>10.1226</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.2615</v>
+        <v>-4.2892</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.6265</v>
+        <v>-3.083</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.6354</v>
+        <v>-1.2063</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.5228</v>
+        <v>6.8285</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5587</v>
+        <v>12.2174</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.0814</v>
+        <v>-5.3888</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9315</v>
+        <v>-3.453100000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7493000000000001</v>
+        <v>-0.8552</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6808</v>
+        <v>-2.5979</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.071400000000001</v>
+        <v>6.829799999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.366</v>
+        <v>4.5685</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7055</v>
+        <v>2.2614</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4175000000000003</v>
+        <v>7.082999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9705999999999999</v>
+        <v>4.6398</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5530999999999999</v>
+        <v>2.4433</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.6538</v>
+        <v>-0.2532000000000003</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3952</v>
+        <v>-0.07120000000000004</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.2585</v>
+        <v>-0.1817999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8437</v>
+        <v>1.2147</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.458</v>
+        <v>-7.2883</v>
       </c>
       <c r="R9" t="n">
-        <v>4.3017</v>
+        <v>8.503</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3119000000000001</v>
+        <v>-5.8291</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4463</v>
+        <v>-2.2488</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7583</v>
+        <v>-3.5803</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6081</v>
+        <v>-5.6686</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1785</v>
+        <v>1.5987</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5704</v>
+        <v>-7.2674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2454</v>
+        <v>-5.6978</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.092499999999999</v>
+        <v>-0.7405999999999997</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.153</v>
+        <v>-4.957199999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9381</v>
+        <v>-7.9562</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.153</v>
+        <v>-4.7854</v>
       </c>
       <c r="I10" t="n">
-        <v>6.091199999999999</v>
+        <v>-3.171</v>
       </c>
       <c r="J10" t="n">
-        <v>7.1858</v>
+        <v>-2.2975</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2825</v>
+        <v>-2.854</v>
       </c>
       <c r="L10" t="n">
-        <v>9.468299999999999</v>
+        <v>0.5567</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.2477</v>
+        <v>-5.6588</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8706</v>
+        <v>-1.9312</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.3769</v>
+        <v>-3.7276</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.2182</v>
+        <v>2.4294</v>
       </c>
       <c r="Q10" t="n">
-        <v>-17.8219</v>
+        <v>-2.4296</v>
       </c>
       <c r="R10" t="n">
-        <v>8.6036</v>
+        <v>4.859</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.4163</v>
+        <v>-0.3029</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.0501</v>
+        <v>1.7278</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3661</v>
+        <v>-2.0306</v>
       </c>
       <c r="V10" t="n">
-        <v>6.4509</v>
+        <v>0.1318000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>11.5937</v>
+        <v>2.2584</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.1429</v>
+        <v>-2.1266</v>
       </c>
     </row>
     <row r="11">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.1126</v>
+        <v>-7.0335</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3411</v>
+        <v>-6.3237</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.771500000000001</v>
+        <v>-0.7098</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.537</v>
+        <v>-5.5589</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5201</v>
+        <v>-0.7481999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.0169</v>
+        <v>-4.8106</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9395</v>
+        <v>-2.5406</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.017</v>
+        <v>-0.3180000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.9225</v>
+        <v>-2.2227</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.5974</v>
+        <v>-3.0183</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5031</v>
+        <v>-0.43</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.0943</v>
+        <v>-2.588</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8679</v>
+        <v>2.4294</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2533</v>
+        <v>-3.2393</v>
       </c>
       <c r="R11" t="n">
-        <v>5.1212</v>
+        <v>5.668699999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4056999999999999</v>
+        <v>-0.5631</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3903</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.01540000000000002</v>
+        <v>0.2318000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.0379</v>
+        <v>-3.341</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.2799</v>
+        <v>-3.5919</v>
       </c>
     </row>
     <row r="12">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.7085</v>
+        <v>-21.4438</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.2555</v>
+        <v>-19.0961</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4529</v>
+        <v>-2.3475</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.1639</v>
+        <v>-15.5232</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.4018</v>
+        <v>-4.8596</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.7623</v>
+        <v>-10.6636</v>
       </c>
       <c r="J12" t="n">
-        <v>-8.7324</v>
+        <v>-11.1958</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1142</v>
+        <v>-1.942</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.6184</v>
+        <v>-9.2537</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.4316</v>
+        <v>-4.327500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2877</v>
+        <v>-2.9176</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1438</v>
+        <v>-1.4099</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8679</v>
+        <v>-3.4417</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.4472</v>
+        <v>-11.3374</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5793</v>
+        <v>7.8957</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.02590000000000003</v>
+        <v>-0.6175</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6693</v>
+        <v>1.1495</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6953</v>
+        <v>-1.7671</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6505999999999998</v>
+        <v>-1.8613</v>
       </c>
       <c r="W12" t="n">
-        <v>2.255</v>
+        <v>2.2872</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.9056</v>
+        <v>-4.1485</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.907</v>
+        <v>-1.597899999999996</v>
       </c>
       <c r="E13" t="n">
-        <v>4.578199999999995</v>
+        <v>-4.125499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.671400000000002</v>
+        <v>2.528</v>
       </c>
       <c r="G13" t="n">
-        <v>8.965999999999999</v>
+        <v>13.00969999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>5.711200000000003</v>
+        <v>9.299799999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2544</v>
+        <v>3.710500000000003</v>
       </c>
       <c r="J13" t="n">
-        <v>43.1597</v>
+        <v>48.058</v>
       </c>
       <c r="K13" t="n">
-        <v>18.6955</v>
+        <v>24.7279</v>
       </c>
       <c r="L13" t="n">
-        <v>24.4636</v>
+        <v>23.3303</v>
       </c>
       <c r="M13" t="n">
-        <v>-34.1931</v>
+        <v>-35.0484</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.9837</v>
+        <v>-15.4281</v>
       </c>
       <c r="O13" t="n">
-        <v>-21.2082</v>
+        <v>-19.6197</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.120999999999999</v>
+        <v>-5.061399999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-72.72070000000001</v>
+        <v>-85.0304</v>
       </c>
       <c r="R13" t="n">
-        <v>67.5994</v>
+        <v>79.9691</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.855799999999999</v>
+        <v>-8.7285</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1377</v>
+        <v>-4.3802</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.718499999999999</v>
+        <v>-4.348699999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>6.9179</v>
+        <v>-0.8175000000000017</v>
       </c>
       <c r="W13" t="n">
-        <v>35.2781</v>
+        <v>37.2251</v>
       </c>
       <c r="X13" t="n">
-        <v>-28.36</v>
+        <v>-38.0429</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>17.5439</v>
+        <v>15.85</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1928</v>
+        <v>14.776</v>
       </c>
       <c r="F2" t="n">
-        <v>9.351000000000001</v>
+        <v>1.0741</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8076</v>
+        <v>22.6653</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1138</v>
+        <v>10.8111</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6940000000000002</v>
+        <v>11.8543</v>
       </c>
       <c r="J2" t="n">
-        <v>5.278899999999999</v>
+        <v>27.9416</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1284</v>
+        <v>14.336</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1505</v>
+        <v>13.6055</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4713</v>
+        <v>-5.2762</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0147</v>
+        <v>-3.525</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4566</v>
+        <v>-1.7512</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6442</v>
+        <v>-3.4418</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.693199999999999</v>
+        <v>-13.9692</v>
       </c>
       <c r="R2" t="n">
-        <v>11.3374</v>
+        <v>10.5276</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6467</v>
+        <v>-0.3738000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7699</v>
+        <v>-0.4513</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8765000000000001</v>
+        <v>0.07750000000000012</v>
       </c>
       <c r="V2" t="n">
-        <v>9.445599999999999</v>
+        <v>-2.9999</v>
       </c>
       <c r="W2" t="n">
-        <v>9.837</v>
+        <v>1.2545</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3913999999999999</v>
+        <v>-4.2545</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>13.5187</v>
+        <v>15.7462</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6441</v>
+        <v>7.4437</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8746</v>
+        <v>8.3024</v>
       </c>
       <c r="G3" t="n">
-        <v>22.6653</v>
+        <v>2.8076</v>
       </c>
       <c r="H3" t="n">
-        <v>10.8111</v>
+        <v>2.1138</v>
       </c>
       <c r="I3" t="n">
-        <v>11.8543</v>
+        <v>0.6940000000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>27.9416</v>
+        <v>5.278899999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>14.336</v>
+        <v>3.1284</v>
       </c>
       <c r="L3" t="n">
-        <v>13.6055</v>
+        <v>2.1505</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.2762</v>
+        <v>-2.4713</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.525</v>
+        <v>-1.0147</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7512</v>
+        <v>-1.4566</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.4418</v>
+        <v>3.6442</v>
       </c>
       <c r="Q3" t="n">
-        <v>-13.9692</v>
+        <v>-7.693199999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>10.5276</v>
+        <v>11.3374</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.705</v>
+        <v>-0.1510999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.5831</v>
+        <v>0.02100000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8780000000000001</v>
+        <v>-0.1721</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.9999</v>
+        <v>9.445599999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2545</v>
+        <v>9.837</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.2545</v>
+        <v>-0.3913999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1082</v>
+        <v>2.7581</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0482</v>
+        <v>1.7831</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1563</v>
+        <v>0.9750999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.999200000000001</v>
+        <v>3.4493</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6907</v>
+        <v>1.2677</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6914999999999999</v>
+        <v>2.1819</v>
       </c>
       <c r="J4" t="n">
-        <v>6.391900000000001</v>
+        <v>2.3564</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3987</v>
+        <v>0.3161</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9932</v>
+        <v>2.0403</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.3927</v>
+        <v>1.0931</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7082</v>
+        <v>0.9514</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.6847</v>
+        <v>0.1417</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2148</v>
+        <v>-0.2025000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.705500000000001</v>
+        <v>-2.2271</v>
       </c>
       <c r="R4" t="n">
-        <v>9.920199999999999</v>
+        <v>2.0246</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0612</v>
+        <v>0.8835999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2616999999999999</v>
+        <v>0.4635</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7996</v>
+        <v>0.4201000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1667</v>
+        <v>-1.3723</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0037</v>
+        <v>1.1902</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.1705</v>
+        <v>-2.5625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6484</v>
+        <v>2.3077</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0079</v>
+        <v>2.6843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6406999999999998</v>
+        <v>-0.3767</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4493</v>
+        <v>-1.7513</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2677</v>
+        <v>2.3937</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1819</v>
+        <v>-4.1449</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3564</v>
+        <v>3.1619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3161</v>
+        <v>5.0519</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0403</v>
+        <v>-1.8899</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0931</v>
+        <v>-4.9133</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9514</v>
+        <v>-2.6582</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1417</v>
+        <v>-2.255</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2025000000000001</v>
+        <v>1.6196</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2271</v>
+        <v>-7.4908</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0246</v>
+        <v>9.110300000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2261999999999999</v>
+        <v>2.2529</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3117</v>
+        <v>1.6858</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08560000000000012</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3723</v>
+        <v>0.1863999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1902</v>
+        <v>5.3271</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5625</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.132100000000001</v>
+        <v>1.6783</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7308</v>
+        <v>-1.1345</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5987</v>
+        <v>2.8127</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7513</v>
+        <v>1.999200000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3937</v>
+        <v>2.6907</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.1449</v>
+        <v>-0.6914999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1619</v>
+        <v>6.391900000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>5.0519</v>
+        <v>4.3987</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8899</v>
+        <v>1.9932</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.9133</v>
+        <v>-4.3927</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6582</v>
+        <v>-1.7082</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.255</v>
+        <v>-2.6847</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6196</v>
+        <v>1.2148</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.4908</v>
+        <v>-8.705500000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>9.110300000000001</v>
+        <v>9.920199999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0774</v>
+        <v>0.6311</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7324</v>
+        <v>0.1750999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6550999999999999</v>
+        <v>0.4560000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1863999999999999</v>
+        <v>-2.1667</v>
       </c>
       <c r="W6" t="n">
-        <v>5.3271</v>
+        <v>1.0037</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.1408</v>
+        <v>-3.1705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1576</v>
+        <v>0.5435999999999992</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1.4977</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1576</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1384</v>
+        <v>5.909699999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-4.1525</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1384</v>
+        <v>10.0621</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>11.8782</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-2.029</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>13.9071</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1384</v>
+        <v>-5.9686</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-2.1234</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1384</v>
+        <v>-3.845</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-10.5275</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-20.65</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>10.1226</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0192</v>
+        <v>-1.6671</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-1.9481</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0192</v>
+        <v>0.2807</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.8285</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>12.2174</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-5.3888</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0786</v>
+        <v>0.1864</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3626999999999998</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4411</v>
+        <v>0.1864</v>
       </c>
       <c r="G8" t="n">
-        <v>5.909699999999999</v>
+        <v>0.1384</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1525</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>10.0621</v>
+        <v>0.1384</v>
       </c>
       <c r="J8" t="n">
-        <v>11.8782</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.029</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>13.9071</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.9686</v>
+        <v>0.1384</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1234</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.845</v>
+        <v>0.1384</v>
       </c>
       <c r="P8" t="n">
-        <v>-10.5275</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-20.65</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>10.1226</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.2892</v>
+        <v>0.048</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.083</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2063</v>
+        <v>0.048</v>
       </c>
       <c r="V8" t="n">
-        <v>6.8285</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>12.2174</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.3888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.453100000000001</v>
+        <v>-0.04059999999999953</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8552</v>
+        <v>0.8632</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5979</v>
+        <v>-0.9036000000000002</v>
       </c>
       <c r="G9" t="n">
         <v>6.829799999999999</v>
@@ -1156,13 +1156,13 @@
         <v>8.503</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.8291</v>
+        <v>-2.4165</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.2488</v>
+        <v>-0.5304</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.5803</v>
+        <v>-1.886</v>
       </c>
       <c r="V9" t="n">
         <v>-5.6686</v>
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6978</v>
+        <v>-6.3437</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7405999999999997</v>
+        <v>-2.1301</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.957199999999999</v>
+        <v>-4.213699999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-7.9562</v>
@@ -1234,13 +1234,13 @@
         <v>4.859</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3029</v>
+        <v>-0.9487</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7278</v>
+        <v>0.3384</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.0306</v>
+        <v>-1.2872</v>
       </c>
       <c r="V10" t="n">
         <v>0.1318000000000001</v>
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0335</v>
+        <v>-6.4371</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3237</v>
+        <v>-5.8601</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7098</v>
+        <v>-0.5771000000000002</v>
       </c>
       <c r="G11" t="n">
         <v>-5.5589</v>
@@ -1312,13 +1312,13 @@
         <v>5.668699999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5631</v>
+        <v>0.03339999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.331</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2318000000000001</v>
+        <v>0.3645</v>
       </c>
       <c r="V11" t="n">
         <v>-3.341</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-21.4438</v>
+        <v>-20.5483</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.0961</v>
+        <v>-19.5667</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3475</v>
+        <v>-0.9814000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>-15.5232</v>
@@ -1390,13 +1390,13 @@
         <v>7.8957</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6175</v>
+        <v>0.2779000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1495</v>
+        <v>0.6789999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7671</v>
+        <v>-0.401</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8613</v>
@@ -1423,22 +1423,22 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.597899999999996</v>
+        <v>5.700600000000005</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.125499999999999</v>
+        <v>0.3566000000000003</v>
       </c>
       <c r="F13" t="n">
-        <v>2.528</v>
+        <v>5.344100000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>13.00969999999999</v>
+        <v>13.0097</v>
       </c>
       <c r="H13" t="n">
-        <v>9.299799999999998</v>
+        <v>9.299800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3.710500000000003</v>
+        <v>3.7105</v>
       </c>
       <c r="J13" t="n">
         <v>48.058</v>
@@ -1468,13 +1468,13 @@
         <v>79.9691</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.7285</v>
+        <v>-1.430300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.3802</v>
+        <v>0.1020000000000004</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.348699999999999</v>
+        <v>-1.5325</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8175000000000017</v>
